--- a/data/mapas/Mapa_de_Carrera_Lengua_y_Literatura.xlsx
+++ b/data/mapas/Mapa_de_Carrera_Lengua_y_Literatura.xlsx
@@ -555,13 +555,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K59"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="J2" s="5" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="J3" s="5">
-        <f>COUNTIF(B6:B59, "SI")</f>
+        <f>COUNTIF(B6:B42, "SI")</f>
         <v/>
       </c>
     </row>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="J4" s="5">
-        <f>COUNTIF(C6:C59, "SI")</f>
+        <f>COUNTIF(C6:C42, "SI")</f>
         <v/>
       </c>
     </row>
@@ -667,14 +667,14 @@
         </is>
       </c>
       <c r="J5" s="5">
-        <f>COUNTIF(F6:F59, "ADEUDA FINAL")</f>
+        <f>COUNTIF(F6:F42, "ADEUDA FINAL")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Pedagogía</t>
+          <t>Lingüística General I</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -710,14 +710,14 @@
         </is>
       </c>
       <c r="J6" s="12">
-        <f>COUNTIF(B6:B59, "SI")/48</f>
+        <f>COUNTIF(B6:B42, "SI")/33</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Didáctica General</t>
+          <t>Gramática Española I</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -753,14 +753,14 @@
         </is>
       </c>
       <c r="J7" s="12">
-        <f>COUNTIF(C6:C59, "SI")/48</f>
+        <f>COUNTIF(C6:C42, "SI")/33</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Introducción a la Disciplina</t>
+          <t>Teoría y Análisis Literario I</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -794,7 +794,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Práctica Docente I</t>
+          <t>Literatura Española I (Medieval y Siglo de Oro)</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -831,10 +831,37 @@
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>📌 2° AÑO</t>
-        </is>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Pedagogía</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>1° Año</t>
+        </is>
+      </c>
+      <c r="E10" s="10">
+        <f>IF(B10="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F10" s="10">
+        <f>IF(C10="SI", "APROBADO", IF(B10="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G10" s="11">
+        <f>IF(C10="SI", "🟢 Aprobada", IF(B10="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
@@ -845,7 +872,7 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Psicología Educacional</t>
+          <t>Lectura, Escritura y Oralidad I (LEO 1)</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -860,7 +887,7 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E11" s="10">
@@ -884,7 +911,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Sociología de la Educación</t>
+          <t>Trabajo de Campo I</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -899,7 +926,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E12" s="10">
@@ -921,37 +948,10 @@
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Sujetos de la Educación</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>2° Año</t>
-        </is>
-      </c>
-      <c r="E13" s="10">
-        <f>IF(B13="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F13" s="10">
-        <f>IF(C13="SI", "APROBADO", IF(B13="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G13" s="11">
-        <f>IF(C13="SI", "🟢 Aprobada", IF(B13="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>📌 2° AÑO</t>
+        </is>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Práctica Docente II</t>
+          <t>Lingüística General II</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
@@ -999,10 +999,37 @@
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>📌 3° AÑO</t>
-        </is>
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Gramática Española II</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>2° Año</t>
+        </is>
+      </c>
+      <c r="E15" s="10">
+        <f>IF(B15="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F15" s="10">
+        <f>IF(C15="SI", "APROBADO", IF(B15="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G15" s="11">
+        <f>IF(C15="SI", "🟢 Aprobada", IF(B15="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
       <c r="I15" s="14" t="inlineStr">
         <is>
@@ -1013,7 +1040,7 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Historia Social de la Educación</t>
+          <t>Teoría y Análisis Literario II</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
@@ -1028,7 +1055,7 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E16" s="10">
@@ -1047,7 +1074,7 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Residencia I</t>
+          <t>Literatura Española II</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -1062,7 +1089,7 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E17" s="10">
@@ -1081,7 +1108,7 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Espacio de Definición Institucional</t>
+          <t>Literatura Latinoamericana I</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -1096,7 +1123,7 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E18" s="10">
@@ -1115,7 +1142,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Práctica Docente III</t>
+          <t>Didáctica General</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -1130,7 +1157,7 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E19" s="10">
@@ -1146,17 +1173,44 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>📌 4° AÑO</t>
-        </is>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Psicología Educacional</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>2° Año</t>
+        </is>
+      </c>
+      <c r="E20" s="10">
+        <f>IF(B20="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F20" s="10">
+        <f>IF(C20="SI", "APROBADO", IF(B20="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G20" s="11">
+        <f>IF(C20="SI", "🟢 Aprobada", IF(B20="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Residencia II / Taller de Cierre</t>
+          <t>Sujetos de la Educación</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -1171,7 +1225,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E21" s="10">
@@ -1190,7 +1244,7 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Ética y Trabajo Docente</t>
+          <t>Trabajo de Campo II</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
@@ -1205,7 +1259,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E22" s="10">
@@ -1221,44 +1275,17 @@
         <v/>
       </c>
     </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>Investigación Educativa</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>4° Año</t>
-        </is>
-      </c>
-      <c r="E23" s="10">
-        <f>IF(B23="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F23" s="10">
-        <f>IF(C23="SI", "APROBADO", IF(B23="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G23" s="11">
-        <f>IF(C23="SI", "🟢 Aprobada", IF(B23="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>📌 3° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Práctica Docente IV</t>
+          <t>Historia de la Lengua Española</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
@@ -1273,7 +1300,7 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E24" s="10">
@@ -1289,17 +1316,44 @@
         <v/>
       </c>
     </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>📌 5° AÑO (NIVEL SUPERIOR / TRAMO SUPERIOR)</t>
-        </is>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Literatura Latinoamericana II</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>3° Año</t>
+        </is>
+      </c>
+      <c r="E25" s="10">
+        <f>IF(B25="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F25" s="10">
+        <f>IF(C25="SI", "APROBADO", IF(B25="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G25" s="11">
+        <f>IF(C25="SI", "🟢 Aprobada", IF(B25="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Especialización Superior I</t>
+          <t>Literatura Argentina I</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -1314,7 +1368,7 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E26" s="10">
@@ -1333,7 +1387,7 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Taller de Investigación Aplicada</t>
+          <t>Didáctica de la Lengua y la Literatura I</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -1348,7 +1402,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E27" s="10">
@@ -1367,7 +1421,7 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Didáctica de Nivel Superior</t>
+          <t>Historia Social de la Educación</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -1382,7 +1436,7 @@
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E28" s="10">
@@ -1401,7 +1455,7 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Práctica de Nivel Superior I</t>
+          <t>Derechos Humanos, Sociedad y Estado</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
@@ -1416,7 +1470,7 @@
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E29" s="10">
@@ -1432,51 +1486,51 @@
         <v/>
       </c>
     </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>📌 6° AÑO (NIVEL SUPERIOR / TRAMO SUPERIOR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>Seminario de Especialización Superior II</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
-        </is>
-      </c>
-      <c r="E31" s="10">
-        <f>IF(B31="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F31" s="10">
-        <f>IF(C31="SI", "APROBADO", IF(B31="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G31" s="11">
-        <f>IF(C31="SI", "🟢 Aprobada", IF(B31="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Construcción de la Práctica Docente I</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>3° Año</t>
+        </is>
+      </c>
+      <c r="E30" s="10">
+        <f>IF(B30="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F30" s="10">
+        <f>IF(C30="SI", "APROBADO", IF(B30="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G30" s="11">
+        <f>IF(C30="SI", "🟢 Aprobada", IF(B30="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>📌 4° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>Tesis / Trabajo Final de Licenciatura</t>
+          <t>Literatura Argentina II</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -1491,7 +1545,7 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E32" s="10">
@@ -1510,7 +1564,7 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>Práctica de Nivel Superior II</t>
+          <t>Literaturas Extranjeras Clásicas y Modernas</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -1525,7 +1579,7 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E33" s="10">
@@ -1544,7 +1598,7 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>Acreditación de Residencia Superior</t>
+          <t>Semiótica y Análisis del Discurso</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
@@ -1559,7 +1613,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E34" s="10">
@@ -1575,17 +1629,44 @@
         <v/>
       </c>
     </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>📌 GENERAL / OPTATIVAS</t>
-        </is>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Didáctica de la Lengua y la Literatura II</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E35" s="10">
+        <f>IF(B35="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F35" s="10">
+        <f>IF(C35="SI", "APROBADO", IF(B35="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G35" s="11">
+        <f>IF(C35="SI", "🟢 Aprobada", IF(B35="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>Educación SEXUAL INTEGRAL</t>
+          <t>Educación Sexual Integral (ESI)</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
@@ -1600,7 +1681,7 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>General / Optativas</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E36" s="10">
@@ -1619,7 +1700,7 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>Estudio de la Diversidad Lingüística</t>
+          <t>Ética y Trabajo Docente</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
@@ -1634,7 +1715,7 @@
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>General / Optativas</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E37" s="10">
@@ -1653,7 +1734,7 @@
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>Gramática HISTORICA</t>
+          <t>Residencia y Construcción de la Práctica Docente II</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
@@ -1668,7 +1749,7 @@
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>General / Optativas</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E38" s="10">
@@ -1684,44 +1765,17 @@
         <v/>
       </c>
     </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>Griego II</t>
-        </is>
-      </c>
-      <c r="B39" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C39" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D39" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E39" s="10">
-        <f>IF(B39="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F39" s="10">
-        <f>IF(C39="SI", "APROBADO", IF(B39="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G39" s="11">
-        <f>IF(C39="SI", "🟢 Aprobada", IF(B39="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>📌 TRAMO SUPERIOR / SEMINARIOS</t>
+        </is>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>Historia del Arte</t>
+          <t>Seminario de Literatura Argentina y Latinoamericana</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
@@ -1736,7 +1790,7 @@
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>General / Optativas</t>
+          <t>Tramo Superior / Seminarios</t>
         </is>
       </c>
       <c r="E40" s="10">
@@ -1755,7 +1809,7 @@
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>Int. Estud. del Lenguaje y Elem. Semiol</t>
+          <t>Seminario de Lingüística Aplicada</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
@@ -1770,7 +1824,7 @@
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>General / Optativas</t>
+          <t>Tramo Superior / Seminarios</t>
         </is>
       </c>
       <c r="E41" s="10">
@@ -1789,7 +1843,7 @@
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>Latin II</t>
+          <t>Taller de Escritura Creativa y Académica</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
@@ -1804,7 +1858,7 @@
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>General / Optativas</t>
+          <t>Tramo Superior / Seminarios</t>
         </is>
       </c>
       <c r="E42" s="10">
@@ -1820,606 +1874,26 @@
         <v/>
       </c>
     </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="8" t="inlineStr">
-        <is>
-          <t>Latin III</t>
-        </is>
-      </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D43" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E43" s="10">
-        <f>IF(B43="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F43" s="10">
-        <f>IF(C43="SI", "APROBADO", IF(B43="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G43" s="11">
-        <f>IF(C43="SI", "🟢 Aprobada", IF(B43="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="8" t="inlineStr">
-        <is>
-          <t>Lectura Escritura y Oralidad II</t>
-        </is>
-      </c>
-      <c r="B44" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D44" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E44" s="10">
-        <f>IF(B44="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F44" s="10">
-        <f>IF(C44="SI", "APROBADO", IF(B44="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G44" s="11">
-        <f>IF(C44="SI", "🟢 Aprobada", IF(B44="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="8" t="inlineStr">
-        <is>
-          <t>Lengua y Lit. Latinas y Su Ens. Niv, M. y Sup</t>
-        </is>
-      </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D45" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E45" s="10">
-        <f>IF(B45="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F45" s="10">
-        <f>IF(C45="SI", "APROBADO", IF(B45="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G45" s="11">
-        <f>IF(C45="SI", "🟢 Aprobada", IF(B45="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="8" t="inlineStr">
-        <is>
-          <t>Literatura Argentina</t>
-        </is>
-      </c>
-      <c r="B46" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C46" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D46" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E46" s="10">
-        <f>IF(B46="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F46" s="10">
-        <f>IF(C46="SI", "APROBADO", IF(B46="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G46" s="11">
-        <f>IF(C46="SI", "🟢 Aprobada", IF(B46="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="8" t="inlineStr">
-        <is>
-          <t>Literatura Española del Siglo de Oro</t>
-        </is>
-      </c>
-      <c r="B47" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C47" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D47" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E47" s="10">
-        <f>IF(B47="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F47" s="10">
-        <f>IF(C47="SI", "APROBADO", IF(B47="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G47" s="11">
-        <f>IF(C47="SI", "🟢 Aprobada", IF(B47="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="8" t="inlineStr">
-        <is>
-          <t>Literatura, Cine y Otros Lenguajes</t>
-        </is>
-      </c>
-      <c r="B48" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C48" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D48" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E48" s="10">
-        <f>IF(B48="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F48" s="10">
-        <f>IF(C48="SI", "APROBADO", IF(B48="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G48" s="11">
-        <f>IF(C48="SI", "🟢 Aprobada", IF(B48="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="8" t="inlineStr">
-        <is>
-          <t>METODOLOGIA ESPECIAL y Residencia</t>
-        </is>
-      </c>
-      <c r="B49" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C49" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D49" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E49" s="10">
-        <f>IF(B49="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F49" s="10">
-        <f>IF(C49="SI", "APROBADO", IF(B49="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G49" s="11">
-        <f>IF(C49="SI", "🟢 Aprobada", IF(B49="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="8" t="inlineStr">
-        <is>
-          <t>Sem. Rep. y Proy. Discursos de la Antig</t>
-        </is>
-      </c>
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C50" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D50" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E50" s="10">
-        <f>IF(B50="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F50" s="10">
-        <f>IF(C50="SI", "APROBADO", IF(B50="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G50" s="11">
-        <f>IF(C50="SI", "🟢 Aprobada", IF(B50="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="8" t="inlineStr">
-        <is>
-          <t>Seminario de Literatura Rusa</t>
-        </is>
-      </c>
-      <c r="B51" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C51" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D51" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E51" s="10">
-        <f>IF(B51="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F51" s="10">
-        <f>IF(C51="SI", "APROBADO", IF(B51="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G51" s="11">
-        <f>IF(C51="SI", "🟢 Aprobada", IF(B51="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="8" t="inlineStr">
-        <is>
-          <t>Seminario Lenguaje, Sociedad y Educac</t>
-        </is>
-      </c>
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C52" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D52" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E52" s="10">
-        <f>IF(B52="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F52" s="10">
-        <f>IF(C52="SI", "APROBADO", IF(B52="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G52" s="11">
-        <f>IF(C52="SI", "🟢 Aprobada", IF(B52="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="8" t="inlineStr">
-        <is>
-          <t>Sujeto de Nivel</t>
-        </is>
-      </c>
-      <c r="B53" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C53" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D53" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E53" s="10">
-        <f>IF(B53="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F53" s="10">
-        <f>IF(C53="SI", "APROBADO", IF(B53="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G53" s="11">
-        <f>IF(C53="SI", "🟢 Aprobada", IF(B53="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="8" t="inlineStr">
-        <is>
-          <t>TALLER DE Gramática Y LINGÜÍSTICA</t>
-        </is>
-      </c>
-      <c r="B54" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C54" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D54" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E54" s="10">
-        <f>IF(B54="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F54" s="10">
-        <f>IF(C54="SI", "APROBADO", IF(B54="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G54" s="11">
-        <f>IF(C54="SI", "🟢 Aprobada", IF(B54="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="8" t="inlineStr">
-        <is>
-          <t>Taller de Lect. Escritura y Oralidad</t>
-        </is>
-      </c>
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C55" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D55" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E55" s="10">
-        <f>IF(B55="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F55" s="10">
-        <f>IF(C55="SI", "APROBADO", IF(B55="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G55" s="11">
-        <f>IF(C55="SI", "🟢 Aprobada", IF(B55="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="8" t="inlineStr">
-        <is>
-          <t>Taller de Lect. Escritura y Oralidad I : Generos Academicos</t>
-        </is>
-      </c>
-      <c r="B56" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C56" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D56" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E56" s="10">
-        <f>IF(B56="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F56" s="10">
-        <f>IF(C56="SI", "APROBADO", IF(B56="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G56" s="11">
-        <f>IF(C56="SI", "🟢 Aprobada", IF(B56="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="8" t="inlineStr">
-        <is>
-          <t>Taller de Lectura Esc y Oralidad I</t>
-        </is>
-      </c>
-      <c r="B57" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C57" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D57" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E57" s="10">
-        <f>IF(B57="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F57" s="10">
-        <f>IF(C57="SI", "APROBADO", IF(B57="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G57" s="11">
-        <f>IF(C57="SI", "🟢 Aprobada", IF(B57="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="8" t="inlineStr">
-        <is>
-          <t>TALLER DE LITER. Y Teoría LITERARIA</t>
-        </is>
-      </c>
-      <c r="B58" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C58" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D58" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E58" s="10">
-        <f>IF(B58="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F58" s="10">
-        <f>IF(C58="SI", "APROBADO", IF(B58="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G58" s="11">
-        <f>IF(C58="SI", "🟢 Aprobada", IF(B58="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="8" t="inlineStr">
-        <is>
-          <t>Taller de Literatura Arg. y Latinoam</t>
-        </is>
-      </c>
-      <c r="B59" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C59" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D59" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E59" s="10">
-        <f>IF(B59="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F59" s="10">
-        <f>IF(C59="SI", "APROBADO", IF(B59="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G59" s="11">
-        <f>IF(C59="SI", "🟢 Aprobada", IF(B59="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="I14:J14"/>
+  <mergeCells count="15">
+    <mergeCell ref="A13:G13"/>
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A31:G31"/>
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="I10:J10"/>
-    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A39:G39"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A30:G30"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A15:G15"/>
     <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="I14:J14"/>
     <mergeCell ref="I9:J9"/>
-    <mergeCell ref="A10:G10"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B6 B7 B8 B9 B11 B12 B13 B14 B16 B17 B18 B19 B21 B22 B23 B24 B26 B27 B28 B29 B31 B32 B33 B34 B36 B37 B38 B39 B40 B41 B42 B43 B44 B45 B46 B47 B48 B49 B50 B51 B52 B53 B54 B55 B56 B57 B58 B59 C6 C7 C8 C9 C11 C12 C13 C14 C16 C17 C18 C19 C21 C22 C23 C24 C26 C27 C28 C29 C31 C32 C33 C34 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45 C46 C47 C48 C49 C50 C51 C52 C53 C54 C55 C56 C57 C58 C59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
+    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B14 B15 B16 B17 B18 B19 B20 B21 B22 B24 B25 B26 B27 B28 B29 B30 B32 B33 B34 B35 B36 B37 B38 B40 B41 B42 C6 C7 C8 C9 C10 C11 C12 C14 C15 C16 C17 C18 C19 C20 C21 C22 C24 C25 C26 C27 C28 C29 C30 C32 C33 C34 C35 C36 C37 C38 C40 C41 C42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/mapas/Mapa_de_Carrera_Lengua_y_Literatura.xlsx
+++ b/data/mapas/Mapa_de_Carrera_Lengua_y_Literatura.xlsx
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="J2" s="5" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="J3" s="5">
-        <f>COUNTIF(B6:B42, "SI")</f>
+        <f>COUNTIF(B6:B60, "SI")</f>
         <v/>
       </c>
     </row>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="J4" s="5">
-        <f>COUNTIF(C6:C42, "SI")</f>
+        <f>COUNTIF(C6:C60, "SI")</f>
         <v/>
       </c>
     </row>
@@ -667,14 +667,14 @@
         </is>
       </c>
       <c r="J5" s="5">
-        <f>COUNTIF(F6:F42, "ADEUDA FINAL")</f>
+        <f>COUNTIF(F6:F60, "ADEUDA FINAL")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Lingüística General I</t>
+          <t>Lectura, escritura y oralidad 1: generos académicos</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -710,14 +710,14 @@
         </is>
       </c>
       <c r="J6" s="12">
-        <f>COUNTIF(B6:B42, "SI")/33</f>
+        <f>COUNTIF(B6:B60, "SI")/50</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Gramática Española I</t>
+          <t>Taller de lectura de textos literarios</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -753,14 +753,14 @@
         </is>
       </c>
       <c r="J7" s="12">
-        <f>COUNTIF(C6:C42, "SI")/33</f>
+        <f>COUNTIF(C6:C60, "SI")/50</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Teoría y Análisis Literario I</t>
+          <t>Taller de gramatica y lingüistica</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -794,7 +794,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Literatura Española I (Medieval y Siglo de Oro)</t>
+          <t>Taller de literatura y teoría literaria</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Pedagogía</t>
+          <t>Taller de literatura Argentina y Latinoamericana conectada con la literatura española</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
@@ -872,7 +872,7 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Lectura, Escritura y Oralidad I (LEO 1)</t>
+          <t>Teoría literaria</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -911,7 +911,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Trabajo de Campo I</t>
+          <t>Fílosofia</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -948,10 +948,37 @@
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>📌 2° AÑO</t>
-        </is>
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Introducción al estudio del lenguaje y elemento de semiología</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>1° Año</t>
+        </is>
+      </c>
+      <c r="E13" s="10">
+        <f>IF(B13="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F13" s="10">
+        <f>IF(C13="SI", "APROBADO", IF(B13="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G13" s="11">
+        <f>IF(C13="SI", "🟢 Aprobada", IF(B13="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
@@ -962,7 +989,7 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Lingüística General II</t>
+          <t>Introducción a la lengua y la literatura latina</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
@@ -977,7 +1004,7 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E14" s="10">
@@ -1001,7 +1028,7 @@
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Gramática Española II</t>
+          <t>Latín 1 y literatura latina</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
@@ -1016,7 +1043,7 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E15" s="10">
@@ -1040,7 +1067,7 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Teoría y Análisis Literario II</t>
+          <t>Pedagogía</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
@@ -1055,7 +1082,7 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E16" s="10">
@@ -1074,7 +1101,7 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Literatura Española II</t>
+          <t>Psicología educacional</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -1089,7 +1116,7 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E17" s="10">
@@ -1108,7 +1135,7 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Literatura Latinoamericana I</t>
+          <t>Sujetos del nivel medio y superior</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -1123,7 +1150,7 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E18" s="10">
@@ -1139,44 +1166,17 @@
         <v/>
       </c>
     </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>Didáctica General</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>2° Año</t>
-        </is>
-      </c>
-      <c r="E19" s="10">
-        <f>IF(B19="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F19" s="10">
-        <f>IF(C19="SI", "APROBADO", IF(B19="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G19" s="11">
-        <f>IF(C19="SI", "🟢 Aprobada", IF(B19="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>📌 2° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Psicología Educacional</t>
+          <t>Lectura, escritura y oralidad 2: generos e intercursividad</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
@@ -1210,7 +1210,7 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Sujetos de la Educación</t>
+          <t>Gramática 1</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -1244,7 +1244,7 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Trabajo de Campo II</t>
+          <t>Literatura francesa e italiana</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
@@ -1275,17 +1275,44 @@
         <v/>
       </c>
     </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>📌 3° AÑO</t>
-        </is>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Historia del arte</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>2° Año</t>
+        </is>
+      </c>
+      <c r="E23" s="10">
+        <f>IF(B23="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F23" s="10">
+        <f>IF(C23="SI", "APROBADO", IF(B23="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G23" s="11">
+        <f>IF(C23="SI", "🟢 Aprobada", IF(B23="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Historia de la Lengua Española</t>
+          <t>Latín 2 y literatura latina</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
@@ -1300,7 +1327,7 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E24" s="10">
@@ -1319,7 +1346,7 @@
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>Literatura Latinoamericana II</t>
+          <t>Didáctica general</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
@@ -1334,7 +1361,7 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E25" s="10">
@@ -1353,7 +1380,7 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Literatura Argentina I</t>
+          <t>La lectura y la escritura en la educación formal y no formal</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -1368,7 +1395,7 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E26" s="10">
@@ -1387,7 +1414,7 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Didáctica de la Lengua y la Literatura I</t>
+          <t>Lectocomprensión de lengua extranjera 1</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -1402,7 +1429,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E27" s="10">
@@ -1421,7 +1448,7 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Historia Social de la Educación</t>
+          <t>Lectocomprensión de lengua extranjera 2</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -1436,7 +1463,7 @@
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E28" s="10">
@@ -1455,7 +1482,7 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Derechos Humanos, Sociedad y Estado</t>
+          <t>Nuevas tecnologias</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
@@ -1470,7 +1497,7 @@
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E29" s="10">
@@ -1486,51 +1513,51 @@
         <v/>
       </c>
     </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>Construcción de la Práctica Docente I</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr">
-        <is>
-          <t>3° Año</t>
-        </is>
-      </c>
-      <c r="E30" s="10">
-        <f>IF(B30="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F30" s="10">
-        <f>IF(C30="SI", "APROBADO", IF(B30="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G30" s="11">
-        <f>IF(C30="SI", "🟢 Aprobada", IF(B30="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>📌 4° AÑO</t>
-        </is>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>📌 TRAMO SUPERIOR / SEMINARIOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Lenguaje, sociedad y educacíon</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>Tramo Superior / Seminarios</t>
+        </is>
+      </c>
+      <c r="E31" s="10">
+        <f>IF(B31="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F31" s="10">
+        <f>IF(C31="SI", "APROBADO", IF(B31="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G31" s="11">
+        <f>IF(C31="SI", "🟢 Aprobada", IF(B31="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>Literatura Argentina II</t>
+          <t>Canon literario, canon escolar y formación del gusto</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -1545,7 +1572,7 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>Tramo Superior / Seminarios</t>
         </is>
       </c>
       <c r="E32" s="10">
@@ -1564,7 +1591,7 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>Literaturas Extranjeras Clásicas y Modernas</t>
+          <t>Representación y proyección de los discrusos de la Antigüedad en la escuela</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -1579,7 +1606,7 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>Tramo Superior / Seminarios</t>
         </is>
       </c>
       <c r="E33" s="10">
@@ -1598,7 +1625,7 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>Semiótica y Análisis del Discurso</t>
+          <t>Retórica y poética</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
@@ -1613,7 +1640,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>Tramo Superior / Seminarios</t>
         </is>
       </c>
       <c r="E34" s="10">
@@ -1632,7 +1659,7 @@
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>Didáctica de la Lengua y la Literatura II</t>
+          <t>Literatura rusa y de otros patrimonios culturales no occidentales</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
@@ -1647,7 +1674,7 @@
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>Tramo Superior / Seminarios</t>
         </is>
       </c>
       <c r="E35" s="10">
@@ -1666,7 +1693,7 @@
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>Educación Sexual Integral (ESI)</t>
+          <t>Análisis del discurso</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
@@ -1681,7 +1708,7 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>Tramo Superior / Seminarios</t>
         </is>
       </c>
       <c r="E36" s="10">
@@ -1700,7 +1727,7 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>Ética y Trabajo Docente</t>
+          <t>Estudios hispánicos</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
@@ -1715,7 +1742,7 @@
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>Tramo Superior / Seminarios</t>
         </is>
       </c>
       <c r="E37" s="10">
@@ -1731,51 +1758,51 @@
         <v/>
       </c>
     </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>Residencia y Construcción de la Práctica Docente II</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D38" s="10" t="inlineStr">
-        <is>
-          <t>4° Año</t>
-        </is>
-      </c>
-      <c r="E38" s="10">
-        <f>IF(B38="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F38" s="10">
-        <f>IF(C38="SI", "APROBADO", IF(B38="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G38" s="11">
-        <f>IF(C38="SI", "🟢 Aprobada", IF(B38="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>📌 TRAMO SUPERIOR / SEMINARIOS</t>
-        </is>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>📌 3° AÑO</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>Gramática 2</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>3° Año</t>
+        </is>
+      </c>
+      <c r="E39" s="10">
+        <f>IF(B39="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F39" s="10">
+        <f>IF(C39="SI", "APROBADO", IF(B39="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G39" s="11">
+        <f>IF(C39="SI", "🟢 Aprobada", IF(B39="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Literatura Argentina y Latinoamericana</t>
+          <t>Literatura en la lengua inglesa y alemana</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
@@ -1790,7 +1817,7 @@
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>Tramo Superior / Seminarios</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E40" s="10">
@@ -1809,7 +1836,7 @@
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Lingüística Aplicada</t>
+          <t>Literatura española del siglo de oro</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
@@ -1824,7 +1851,7 @@
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>Tramo Superior / Seminarios</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E41" s="10">
@@ -1843,7 +1870,7 @@
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>Taller de Escritura Creativa y Académica</t>
+          <t>Latín 3 y literatura latina</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
@@ -1858,7 +1885,7 @@
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>Tramo Superior / Seminarios</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E42" s="10">
@@ -1874,26 +1901,585 @@
         <v/>
       </c>
     </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>Griego 1 y literatura griega</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>3° Año</t>
+        </is>
+      </c>
+      <c r="E43" s="10">
+        <f>IF(B43="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F43" s="10">
+        <f>IF(C43="SI", "APROBADO", IF(B43="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G43" s="11">
+        <f>IF(C43="SI", "🟢 Aprobada", IF(B43="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>Historia de la educación Argentina</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>3° Año</t>
+        </is>
+      </c>
+      <c r="E44" s="10">
+        <f>IF(B44="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F44" s="10">
+        <f>IF(C44="SI", "APROBADO", IF(B44="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G44" s="11">
+        <f>IF(C44="SI", "🟢 Aprobada", IF(B44="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>Sistema y politica educativa</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>3° Año</t>
+        </is>
+      </c>
+      <c r="E45" s="10">
+        <f>IF(B45="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F45" s="10">
+        <f>IF(C45="SI", "APROBADO", IF(B45="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G45" s="11">
+        <f>IF(C45="SI", "🟢 Aprobada", IF(B45="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>📌 4° AÑO</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>Gramática 3</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E47" s="10">
+        <f>IF(B47="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F47" s="10">
+        <f>IF(C47="SI", "APROBADO", IF(B47="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G47" s="11">
+        <f>IF(C47="SI", "🟢 Aprobada", IF(B47="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>Gramática histórica</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E48" s="10">
+        <f>IF(B48="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F48" s="10">
+        <f>IF(C48="SI", "APROBADO", IF(B48="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G48" s="11">
+        <f>IF(C48="SI", "🟢 Aprobada", IF(B48="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>Literatura Argentina</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E49" s="10">
+        <f>IF(B49="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F49" s="10">
+        <f>IF(C49="SI", "APROBADO", IF(B49="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G49" s="11">
+        <f>IF(C49="SI", "🟢 Aprobada", IF(B49="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>Literatura Latinoamericana</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E50" s="10">
+        <f>IF(B50="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F50" s="10">
+        <f>IF(C50="SI", "APROBADO", IF(B50="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G50" s="11">
+        <f>IF(C50="SI", "🟢 Aprobada", IF(B50="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>Lengua y literatura Latinas y su enseñanza en el nivel medio y superior</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E51" s="10">
+        <f>IF(B51="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F51" s="10">
+        <f>IF(C51="SI", "APROBADO", IF(B51="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G51" s="11">
+        <f>IF(C51="SI", "🟢 Aprobada", IF(B51="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>Griego 2 y literatura griega</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E52" s="10">
+        <f>IF(B52="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F52" s="10">
+        <f>IF(C52="SI", "APROBADO", IF(B52="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G52" s="11">
+        <f>IF(C52="SI", "🟢 Aprobada", IF(B52="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>Metodología especial y prácticas de la enseñanza</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E53" s="10">
+        <f>IF(B53="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F53" s="10">
+        <f>IF(C53="SI", "APROBADO", IF(B53="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G53" s="11">
+        <f>IF(C53="SI", "🟢 Aprobada", IF(B53="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>📌 5° AÑO</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>DDHH, sociedad y estado</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E55" s="10">
+        <f>IF(B55="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F55" s="10">
+        <f>IF(C55="SI", "APROBADO", IF(B55="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G55" s="11">
+        <f>IF(C55="SI", "🟢 Aprobada", IF(B55="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>Lingüistica</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E56" s="10">
+        <f>IF(B56="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F56" s="10">
+        <f>IF(C56="SI", "APROBADO", IF(B56="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G56" s="11">
+        <f>IF(C56="SI", "🟢 Aprobada", IF(B56="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>Estudio de la diversidad lingüística y su enseñanza en el nivel medio y superior</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E57" s="10">
+        <f>IF(B57="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F57" s="10">
+        <f>IF(C57="SI", "APROBADO", IF(B57="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G57" s="11">
+        <f>IF(C57="SI", "🟢 Aprobada", IF(B57="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>Problemas de literatura contemporánea en lengua española</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E58" s="10">
+        <f>IF(B58="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F58" s="10">
+        <f>IF(C58="SI", "APROBADO", IF(B58="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G58" s="11">
+        <f>IF(C58="SI", "🟢 Aprobada", IF(B58="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>Literatura, cine y otros lenguajes en los siglos XX y XXI</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E59" s="10">
+        <f>IF(B59="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F59" s="10">
+        <f>IF(C59="SI", "APROBADO", IF(B59="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G59" s="11">
+        <f>IF(C59="SI", "🟢 Aprobada", IF(B59="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>Metodología especial y Residencia</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E60" s="10">
+        <f>IF(B60="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F60" s="10">
+        <f>IF(C60="SI", "APROBADO", IF(B60="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G60" s="11">
+        <f>IF(C60="SI", "🟢 Aprobada", IF(B60="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A13:G13"/>
+  <mergeCells count="16">
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A31:G31"/>
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="I10:J10"/>
-    <mergeCell ref="A39:G39"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="I11:J11"/>
+    <mergeCell ref="A30:G30"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A54:G54"/>
     <mergeCell ref="I13:J13"/>
     <mergeCell ref="I14:J14"/>
+    <mergeCell ref="A19:G19"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A46:G46"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B14 B15 B16 B17 B18 B19 B20 B21 B22 B24 B25 B26 B27 B28 B29 B30 B32 B33 B34 B35 B36 B37 B38 B40 B41 B42 C6 C7 C8 C9 C10 C11 C12 C14 C15 C16 C17 C18 C19 C20 C21 C22 C24 C25 C26 C27 C28 C29 C30 C32 C33 C34 C35 C36 C37 C38 C40 C41 C42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
+    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B20 B21 B22 B23 B24 B25 B26 B27 B28 B29 B31 B32 B33 B34 B35 B36 B37 B39 B40 B41 B42 B43 B44 B45 B47 B48 B49 B50 B51 B52 B53 B55 B56 B57 B58 B59 B60 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C31 C32 C33 C34 C35 C36 C37 C39 C40 C41 C42 C43 C44 C45 C47 C48 C49 C50 C51 C52 C53 C55 C56 C57 C58 C59 C60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
   </dataValidations>
